--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.47980577292376</v>
+        <v>3.490468438100111</v>
       </c>
       <c r="D2" t="n">
-        <v>8.67967050944949</v>
+        <v>1.410446457785542</v>
       </c>
       <c r="E2" t="n">
-        <v>1.906722176440415</v>
+        <v>0.3098423536715675</v>
       </c>
       <c r="F2" t="n">
-        <v>4.538316831473947</v>
+        <v>0.7374764851145166</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.29325012580459</v>
+        <v>4.110153145443246</v>
       </c>
       <c r="D3" t="n">
-        <v>17.75630417239739</v>
+        <v>2.885399428014575</v>
       </c>
       <c r="E3" t="n">
-        <v>1.906722176440415</v>
+        <v>0.3098423536715675</v>
       </c>
       <c r="F3" t="n">
-        <v>4.538316831473947</v>
+        <v>0.7374764851145166</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
